--- a/店家數據/整骨&公園/整骨/全台寵物整骨店家.xlsx
+++ b/店家數據/整骨&公園/整骨/全台寵物整骨店家.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonnie\Desktop\整骨&amp;公園\整骨\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6BC77B6-8BAE-4E59-936F-B15278C1CBEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0FEEFD-5DEE-462D-8438-C0D30F4BFCFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12810" windowHeight="5650" xr2:uid="{E031BE53-3305-44D8-97B5-B54936F9A081}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
-  <si>
-    <t>數量</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>店名</t>
   </si>
@@ -56,29 +53,97 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>整骨</t>
+  </si>
+  <si>
+    <t>https://chastone.com/</t>
+  </si>
+  <si>
+    <t>https://www.vh.ntu.edu.tw/index.php?lang=tw&amp;do=team&amp;id=14</t>
+  </si>
+  <si>
+    <t>https://pethealth.com.tw/tdcpt_directories/%E7%8E%8B%E6%A8%A3%E5%8B%95%E7%89%A9%E9%86%AB%E9%99%A2/</t>
+  </si>
+  <si>
+    <t>狗、貓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>https://www.facebook.com/p/%E5%BE%B7%E6%84%9B%E4%B8%AD%E8%A5%BF%E9%86%AB%E5%8B%95%E7%89%A9%E9%86%AB%E9%99%A2-100064023253115/?locale=zh_TW</t>
-  </si>
-  <si>
-    <t>整骨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中市北屯區昌平路一段95-9號</t>
   </si>
   <si>
     <t>https://www.instagram.com/ny_nick777?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
-  </si>
-  <si>
-    <t>https://chastone.com/</t>
-  </si>
-  <si>
-    <t>https://www.vh.ntu.edu.tw/index.php?lang=tw&amp;do=team&amp;id=14</t>
-  </si>
-  <si>
-    <t>https://pethealth.com.tw/tdcpt_directories/%E7%8E%8B%E6%A8%A3%E5%8B%95%E7%89%A9%E9%86%AB%E9%99%A2/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北市中正區臨沂街66巷3號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>星期一~星期五上午9:00 - 下午12:30 、下午3:00 - 下午9:00
+星期六上午9:00 - 下午12:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>星期一~星期日10:00–20:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NY歪·整復｜AMCT｜體態雕塑平衡｜產後調整</t>
+  </si>
+  <si>
+    <t>確石寵物整脊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>狗、貓、馬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>minyi278@gmail.com</t>
+  </si>
+  <si>
+    <t>台北市大安區基隆路三段153號</t>
+  </si>
+  <si>
+    <t>02-2739-6828 (10線)</t>
+  </si>
+  <si>
+    <t>國立臺灣大學生物資源暨農學院附設動物醫院</t>
+  </si>
+  <si>
+    <t>星期一~星期五08:00–17:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>王樣動物醫院</t>
+  </si>
+  <si>
+    <t>台北市大安區金華街217號</t>
+  </si>
+  <si>
+    <t>星期一~星期三、星期四~星期六10:00–13:30
+16:30–19:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-23570217</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>04-35035057</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -126,6 +191,12 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -158,7 +229,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -178,6 +249,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -495,20 +572,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B9FD1A-6D82-4C1D-8EE3-21AF85EE77B8}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" customWidth="1"/>
-    <col min="4" max="4" width="17.36328125" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" customWidth="1"/>
-    <col min="8" max="8" width="16.36328125" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.90625" customWidth="1"/>
+    <col min="3" max="3" width="28.36328125" customWidth="1"/>
+    <col min="4" max="4" width="24.6328125" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,223 +601,263 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="85" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.4">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4">
+        <v>976295396</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="G4" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5" t="s">
+      <c r="G5" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="68" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G6" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{6D21E6C8-FB97-41BE-B695-BEA4BE059DC6}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{CB76B726-7832-452F-A2FB-37870D790801}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{058356F5-0E91-4AC7-BF29-CF9D28DF8773}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{99A80F86-FE27-4603-92A3-436FF668C7AD}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{D5ED219E-23C5-46CC-91A6-C7324B75A0D7}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{6D21E6C8-FB97-41BE-B695-BEA4BE059DC6}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{CB76B726-7832-452F-A2FB-37870D790801}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{058356F5-0E91-4AC7-BF29-CF9D28DF8773}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{99A80F86-FE27-4603-92A3-436FF668C7AD}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{D5ED219E-23C5-46CC-91A6-C7324B75A0D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
